--- a/Employee_Reports_wi48/Rholie Pacio Casison Q0502.xlsx
+++ b/Employee_Reports_wi48/Rholie Pacio Casison Q0502.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1807,53 +1807,53 @@
       <c r="K28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-041</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>04-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>04-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>10-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1915,11 +1915,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2001,11 +2001,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2038,11 +2038,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7957</v>
+        <v>7954</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7957</v>
+        <v>7954</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7966</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7966</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7950</v>
+        <v>7947</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7978</v>
+        <v>7975</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7978</v>
+        <v>7975</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7950</v>
+        <v>7947</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
